--- a/Bussiness_Logic/generated_reports/Progress_Report_1950f97a-5c0d-4cb6-b831-d8f603bf1c68.xlsx
+++ b/Bussiness_Logic/generated_reports/Progress_Report_1950f97a-5c0d-4cb6-b831-d8f603bf1c68.xlsx
@@ -431,7 +431,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>testing</t>
         </is>
       </c>
     </row>
@@ -455,7 +455,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-31 16:21:25</t>
+          <t>2026-08-06 02:08:52</t>
         </is>
       </c>
     </row>
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>38</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>75.22</v>
+        <v>71.03</v>
       </c>
     </row>
     <row r="10">
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -505,7 +505,11 @@
           <t>Attempted Letters</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>A, Z</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -513,7 +517,11 @@
           <t>Weak Letters</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
